--- a/Results_experiment/exp_1/summary.xlsx
+++ b/Results_experiment/exp_1/summary.xlsx
@@ -447,13 +447,13 @@
         <v>3055</v>
       </c>
       <c r="D2">
-        <v>0.7423725517199598</v>
+        <v>0.7313927162110532</v>
       </c>
       <c r="E2">
-        <v>3.669707690237868</v>
+        <v>3.74709150320205</v>
       </c>
       <c r="F2">
-        <v>2.650510617917474</v>
+        <v>2.685576000148751</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -467,13 +467,13 @@
         <v>3014</v>
       </c>
       <c r="D3">
-        <v>0.7376347157846583</v>
+        <v>0.7099596127126552</v>
       </c>
       <c r="E3">
-        <v>5.538610590554311</v>
+        <v>5.823403529028925</v>
       </c>
       <c r="F3">
-        <v>3.883492889182386</v>
+        <v>4.113746241735878</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -487,13 +487,13 @@
         <v>2753</v>
       </c>
       <c r="D4">
-        <v>0.6774041512520954</v>
+        <v>0.6985529383238822</v>
       </c>
       <c r="E4">
-        <v>5.492905737295827</v>
+        <v>5.30980150788797</v>
       </c>
       <c r="F4">
-        <v>3.978183611307949</v>
+        <v>3.784288273478593</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -507,13 +507,13 @@
         <v>2231</v>
       </c>
       <c r="D5">
-        <v>0.5238289941774861</v>
+        <v>0.5389145853606079</v>
       </c>
       <c r="E5">
-        <v>2.964503294359471</v>
+        <v>2.917166084854278</v>
       </c>
       <c r="F5">
-        <v>2.06615184639191</v>
+        <v>2.061966947294455</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -527,13 +527,13 @@
         <v>1838</v>
       </c>
       <c r="D6">
-        <v>0.6153449796149274</v>
+        <v>0.6008819472168484</v>
       </c>
       <c r="E6">
-        <v>4.108366358256045</v>
+        <v>4.184890971152058</v>
       </c>
       <c r="F6">
-        <v>2.9923282258577</v>
+        <v>3.044653801267724</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -547,13 +547,13 @@
         <v>1534</v>
       </c>
       <c r="D7">
-        <v>0.7596821359425926</v>
+        <v>0.7799855696304062</v>
       </c>
       <c r="E7">
-        <v>3.733079829742719</v>
+        <v>3.571904449020168</v>
       </c>
       <c r="F7">
-        <v>2.696296681980648</v>
+        <v>2.613127421915337</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -567,13 +567,13 @@
         <v>1348</v>
       </c>
       <c r="D8">
-        <v>0.628154446677075</v>
+        <v>0.6226375714059309</v>
       </c>
       <c r="E8">
-        <v>2.933342347216145</v>
+        <v>2.955022451608861</v>
       </c>
       <c r="F8">
-        <v>2.205204328370315</v>
+        <v>2.258449594455737</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -587,13 +587,13 @@
         <v>572</v>
       </c>
       <c r="D9">
-        <v>0.5333349301274359</v>
+        <v>0.5772659703662235</v>
       </c>
       <c r="E9">
-        <v>6.527028418085656</v>
+        <v>6.212214755897373</v>
       </c>
       <c r="F9">
-        <v>4.197667588617491</v>
+        <v>3.905984822433928</v>
       </c>
     </row>
   </sheetData>
